--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Covariance_Matrix_Full_GDP_AR2.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/Tables/Covariance_Matrix_Full_GDP_AR2.xlsx
@@ -414,13 +414,13 @@
         <v>4.09403137442769</v>
       </c>
       <c r="C2">
-        <v>-0.3982709137202943</v>
+        <v>-1.175473750652502</v>
       </c>
       <c r="D2">
-        <v>3.214214824217403</v>
+        <v>3.991417661149609</v>
       </c>
       <c r="E2">
-        <v>4.415022735665294</v>
+        <v>5.192225572597502</v>
       </c>
       <c r="F2">
         <v>0.07727955248269143</v>
@@ -431,19 +431,19 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-0.3982709137202943</v>
+        <v>-1.175473750652502</v>
       </c>
       <c r="C3">
-        <v>0.2207035965959673</v>
+        <v>1.847489229790515</v>
       </c>
       <c r="D3">
-        <v>-0.4460877099421368</v>
+        <v>-2.628464888445638</v>
       </c>
       <c r="E3">
-        <v>-0.468121125426371</v>
+        <v>-2.595968666390769</v>
       </c>
       <c r="F3">
-        <v>-0.1508533848898905</v>
+        <v>-0.4269943140522479</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -451,19 +451,19 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3.214214824217403</v>
+        <v>3.991417661149609</v>
       </c>
       <c r="C4">
-        <v>-0.4460877099421368</v>
+        <v>-2.628464888445638</v>
       </c>
       <c r="D4">
-        <v>3.124908471122024</v>
+        <v>5.862877194934478</v>
       </c>
       <c r="E4">
-        <v>3.725926477964997</v>
+        <v>6.409365564238346</v>
       </c>
       <c r="F4">
-        <v>-0.06562394380545716</v>
+        <v>0.2105169853569004</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -471,19 +471,19 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4.415022735665294</v>
+        <v>5.192225572597502</v>
       </c>
       <c r="C5">
-        <v>-0.468121125426371</v>
+        <v>-2.595968666390769</v>
       </c>
       <c r="D5">
-        <v>3.725926477964997</v>
+        <v>6.409365564238346</v>
       </c>
       <c r="E5">
-        <v>5.061898899397573</v>
+        <v>7.690808348131823</v>
       </c>
       <c r="F5">
-        <v>-0.1787550383059061</v>
+        <v>0.09738589085645138</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -494,13 +494,13 @@
         <v>0.07727955248269143</v>
       </c>
       <c r="C6">
-        <v>-0.1508533848898905</v>
+        <v>-0.4269943140522479</v>
       </c>
       <c r="D6">
-        <v>-0.06562394380545716</v>
+        <v>0.2105169853569004</v>
       </c>
       <c r="E6">
-        <v>-0.1787550383059061</v>
+        <v>0.09738589085645138</v>
       </c>
       <c r="F6">
         <v>0.4068879756784879</v>
